--- a/WritingTips.xlsx
+++ b/WritingTips.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4507"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Correct Agjective Order</t>
   </si>
@@ -46,6 +46,21 @@
   </si>
   <si>
     <t>Purpose or qualifier</t>
+  </si>
+  <si>
+    <t>Writing Fonts</t>
+  </si>
+  <si>
+    <t>Garamond</t>
+  </si>
+  <si>
+    <t>Baskerville</t>
+  </si>
+  <si>
+    <t>Cambria</t>
+  </si>
+  <si>
+    <t>Lora</t>
   </si>
 </sst>
 </file>
@@ -101,6 +116,16 @@
   <tableColumns count="2">
     <tableColumn id="2" name="Order"/>
     <tableColumn id="1" name="Correct Agjective Order"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="D3:D7" totalsRowShown="0">
+  <autoFilter ref="D3:D7"/>
+  <tableColumns count="1">
+    <tableColumn id="1" name="Writing Fonts"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -484,10 +509,43 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="D3:D7"/>
   <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
+  <cols>
+    <col min="4" max="4" width="22.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="4:4">
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="4:4">
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="4:4">
+      <c r="D5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="4:4">
+      <c r="D6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="4:4">
+      <c r="D7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>
 

--- a/WritingTips.xlsx
+++ b/WritingTips.xlsx
@@ -7,7 +7,7 @@
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Grammer" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
